--- a/ITI/MHD/StructureDefinition-IHE.MHD.SimplifiedPublish.DocumentReference.xlsx
+++ b/ITI/MHD/StructureDefinition-IHE.MHD.SimplifiedPublish.DocumentReference.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AQ$56</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AQ$58</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2225" uniqueCount="487">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2302" uniqueCount="498">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>4.2.3</t>
+    <t>4.2.4</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-31T14:38:46-05:00</t>
+    <t>2026-06-15T14:55:16-05:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -546,6 +546,13 @@
     <t>Other identifiers associated with the document, including version independent identifiers.</t>
   </si>
   <si>
+    <t xml:space="preserve">value:type}
+</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
     <t>.id / .setId</t>
   </si>
   <si>
@@ -553,6 +560,38 @@
   </si>
   <si>
     <t>DocumentEntry.entryUUID</t>
+  </si>
+  <si>
+    <t>DocumentReference.identifier:entryUUID</t>
+  </si>
+  <si>
+    <t>entryUUID</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Identifier {https://profiles.ihe.net/ITI/MHD/StructureDefinition/IHE.MHD.EntryUUID.Identifier}
+</t>
+  </si>
+  <si>
+    <t>Business identifier for the DocumentReference</t>
+  </si>
+  <si>
+    <t>The Business identifier for the DocumentReference which maps to the DocumentEntry.entryUUID in XDS. This is used to refer to the DocumentReference itself as a record of the Document's metadata, as opposed to the UniqueId element which identifies the document which is pointed at by the document reference. This element SHALL NOT be provided by the client for simplified publish and will instead be assigned by the server.</t>
+  </si>
+  <si>
+    <t>DocumentReference.identifier:uniqueId</t>
+  </si>
+  <si>
+    <t>uniqueId</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Identifier {https://profiles.ihe.net/ITI/MHD/StructureDefinition/IHE.MHD.UniqueIdIdentifier}
+</t>
+  </si>
+  <si>
+    <t>Unique identifier for the referenced Document</t>
+  </si>
+  <si>
+    <t>The unique identifier for the referenced Document which maps to the DocumentEntry.uniqueId in XDS. This is used to identify the document which is pointed at by the DocumentReference Resource, as opposed to the entryUUID element which identifies the DocumentReference Resource itself. If this element is present, it SHALL be the smae as masterIdentifier.</t>
   </si>
   <si>
     <t>DocumentReference.status</t>
@@ -1107,9 +1146,6 @@
   </si>
   <si>
     <t>Extensions are always sliced by (at least) url</t>
-  </si>
-  <si>
-    <t>open</t>
   </si>
   <si>
     <t>DocumentReference.content.attachment.contentType</t>
@@ -1869,7 +1905,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AQ56"/>
+  <dimension ref="A1:AQ58"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="44.6796875" customWidth="true" bestFit="true"/>
@@ -3291,7 +3327,7 @@
         <v>83</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H12" t="s" s="2">
         <v>82</v>
@@ -3348,16 +3384,14 @@
         <v>82</v>
       </c>
       <c r="AB12" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC12" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>167</v>
+      </c>
+      <c r="AC12" s="2"/>
       <c r="AD12" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE12" t="s" s="2">
-        <v>82</v>
+        <v>168</v>
       </c>
       <c r="AF12" t="s" s="2">
         <v>164</v>
@@ -3381,7 +3415,7 @@
         <v>82</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="AN12" t="s" s="2">
         <v>82</v>
@@ -3390,51 +3424,51 @@
         <v>161</v>
       </c>
       <c r="AP12" t="s" s="2">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="AQ12" t="s" s="2">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>170</v>
-      </c>
-      <c r="C13" s="2"/>
+        <v>164</v>
+      </c>
+      <c r="C13" t="s" s="2">
+        <v>173</v>
+      </c>
       <c r="D13" t="s" s="2">
         <v>82</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I13" t="s" s="2">
-        <v>96</v>
+        <v>82</v>
       </c>
       <c r="J13" t="s" s="2">
         <v>96</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>115</v>
+        <v>174</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="N13" t="s" s="2">
-        <v>173</v>
-      </c>
+        <v>176</v>
+      </c>
+      <c r="N13" s="2"/>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
         <v>82</v>
@@ -3444,7 +3478,7 @@
         <v>82</v>
       </c>
       <c r="S13" t="s" s="2">
-        <v>174</v>
+        <v>82</v>
       </c>
       <c r="T13" t="s" s="2">
         <v>82</v>
@@ -3459,13 +3493,13 @@
         <v>82</v>
       </c>
       <c r="X13" t="s" s="2">
-        <v>175</v>
+        <v>82</v>
       </c>
       <c r="Y13" t="s" s="2">
-        <v>176</v>
+        <v>82</v>
       </c>
       <c r="Z13" t="s" s="2">
-        <v>177</v>
+        <v>82</v>
       </c>
       <c r="AA13" t="s" s="2">
         <v>82</v>
@@ -3483,13 +3517,13 @@
         <v>82</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="AG13" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="AH13" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="AI13" t="s" s="2">
         <v>82</v>
@@ -3498,35 +3532,37 @@
         <v>107</v>
       </c>
       <c r="AK13" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="AL13" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM13" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="AN13" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO13" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="AP13" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="AQ13" t="s" s="2">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="B14" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="C14" t="s" s="2">
         <v>178</v>
       </c>
-      <c r="AL13" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM13" t="s" s="2">
-        <v>179</v>
-      </c>
-      <c r="AN13" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO13" t="s" s="2">
-        <v>180</v>
-      </c>
-      <c r="AP13" t="s" s="2">
-        <v>181</v>
-      </c>
-      <c r="AQ13" t="s" s="2">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="14" hidden="true">
-      <c r="A14" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="B14" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
         <v>82</v>
       </c>
@@ -3535,10 +3571,10 @@
         <v>83</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="H14" t="s" s="2">
-        <v>82</v>
+        <v>96</v>
       </c>
       <c r="I14" t="s" s="2">
         <v>82</v>
@@ -3547,17 +3583,15 @@
         <v>96</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>115</v>
+        <v>179</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>185</v>
-      </c>
-      <c r="N14" t="s" s="2">
-        <v>186</v>
-      </c>
+        <v>181</v>
+      </c>
+      <c r="N14" s="2"/>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
         <v>82</v>
@@ -3582,13 +3616,13 @@
         <v>82</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>175</v>
+        <v>82</v>
       </c>
       <c r="Y14" t="s" s="2">
-        <v>187</v>
+        <v>82</v>
       </c>
       <c r="Z14" t="s" s="2">
-        <v>188</v>
+        <v>82</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>82</v>
@@ -3606,13 +3640,13 @@
         <v>82</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>183</v>
+        <v>164</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH14" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="AI14" t="s" s="2">
         <v>82</v>
@@ -3621,33 +3655,33 @@
         <v>107</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>82</v>
+        <v>157</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>189</v>
+        <v>82</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>190</v>
+        <v>169</v>
       </c>
       <c r="AN14" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO14" t="s" s="2">
-        <v>180</v>
+        <v>161</v>
       </c>
       <c r="AP14" t="s" s="2">
-        <v>191</v>
+        <v>170</v>
       </c>
       <c r="AQ14" t="s" s="2">
-        <v>82</v>
+        <v>171</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>192</v>
+        <v>182</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>192</v>
+        <v>182</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3655,31 +3689,31 @@
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="G15" t="s" s="2">
         <v>95</v>
       </c>
       <c r="H15" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I15" t="s" s="2">
         <v>96</v>
-      </c>
-      <c r="I15" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="J15" t="s" s="2">
         <v>96</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>193</v>
+        <v>115</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>194</v>
+        <v>183</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>195</v>
+        <v>184</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>196</v>
+        <v>185</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -3690,7 +3724,7 @@
         <v>82</v>
       </c>
       <c r="S15" t="s" s="2">
-        <v>82</v>
+        <v>186</v>
       </c>
       <c r="T15" t="s" s="2">
         <v>82</v>
@@ -3705,13 +3739,13 @@
         <v>82</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>119</v>
+        <v>187</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>197</v>
+        <v>188</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>198</v>
+        <v>189</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>82</v>
@@ -3729,10 +3763,10 @@
         <v>82</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>192</v>
+        <v>182</v>
       </c>
       <c r="AG15" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="AH15" t="s" s="2">
         <v>95</v>
@@ -3744,47 +3778,47 @@
         <v>107</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>199</v>
+        <v>190</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>200</v>
+        <v>82</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>201</v>
+        <v>191</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>202</v>
+        <v>82</v>
       </c>
       <c r="AO15" t="s" s="2">
-        <v>203</v>
+        <v>192</v>
       </c>
       <c r="AP15" t="s" s="2">
-        <v>204</v>
+        <v>193</v>
       </c>
       <c r="AQ15" t="s" s="2">
-        <v>205</v>
+        <v>194</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>206</v>
+        <v>195</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>206</v>
+        <v>195</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>207</v>
+        <v>82</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="H16" t="s" s="2">
-        <v>96</v>
+        <v>82</v>
       </c>
       <c r="I16" t="s" s="2">
         <v>82</v>
@@ -3793,16 +3827,16 @@
         <v>96</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>193</v>
+        <v>115</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>208</v>
+        <v>196</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>209</v>
+        <v>197</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>210</v>
+        <v>198</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
@@ -3828,13 +3862,13 @@
         <v>82</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>211</v>
+        <v>187</v>
       </c>
       <c r="Y16" t="s" s="2">
-        <v>212</v>
+        <v>199</v>
       </c>
       <c r="Z16" t="s" s="2">
-        <v>213</v>
+        <v>200</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>82</v>
@@ -3852,13 +3886,13 @@
         <v>82</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>206</v>
+        <v>195</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH16" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="AI16" t="s" s="2">
         <v>82</v>
@@ -3870,30 +3904,30 @@
         <v>82</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>214</v>
+        <v>201</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>215</v>
+        <v>202</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>216</v>
+        <v>82</v>
       </c>
       <c r="AO16" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="AP16" t="s" s="2">
         <v>203</v>
       </c>
-      <c r="AP16" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="AQ16" t="s" s="2">
-        <v>217</v>
+        <v>82</v>
       </c>
     </row>
-    <row r="17" hidden="true">
+    <row r="17">
       <c r="A17" t="s" s="2">
-        <v>218</v>
+        <v>204</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>218</v>
+        <v>204</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3901,13 +3935,13 @@
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="G17" t="s" s="2">
         <v>95</v>
       </c>
       <c r="H17" t="s" s="2">
-        <v>82</v>
+        <v>96</v>
       </c>
       <c r="I17" t="s" s="2">
         <v>82</v>
@@ -3916,15 +3950,17 @@
         <v>96</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>219</v>
+        <v>205</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>220</v>
+        <v>206</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>221</v>
-      </c>
-      <c r="N17" s="2"/>
+        <v>207</v>
+      </c>
+      <c r="N17" t="s" s="2">
+        <v>208</v>
+      </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
         <v>82</v>
@@ -3949,13 +3985,13 @@
         <v>82</v>
       </c>
       <c r="X17" t="s" s="2">
-        <v>82</v>
+        <v>119</v>
       </c>
       <c r="Y17" t="s" s="2">
-        <v>82</v>
+        <v>209</v>
       </c>
       <c r="Z17" t="s" s="2">
-        <v>82</v>
+        <v>210</v>
       </c>
       <c r="AA17" t="s" s="2">
         <v>82</v>
@@ -3973,7 +4009,7 @@
         <v>82</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>218</v>
+        <v>204</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>83</v>
@@ -3988,37 +4024,37 @@
         <v>107</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>222</v>
+        <v>211</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>223</v>
+        <v>212</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>224</v>
+        <v>213</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>225</v>
+        <v>214</v>
       </c>
       <c r="AO17" t="s" s="2">
-        <v>226</v>
+        <v>215</v>
       </c>
       <c r="AP17" t="s" s="2">
-        <v>227</v>
+        <v>216</v>
       </c>
       <c r="AQ17" t="s" s="2">
-        <v>228</v>
+        <v>217</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>229</v>
+        <v>218</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>229</v>
+        <v>218</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
-        <v>230</v>
+        <v>219</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
@@ -4037,16 +4073,16 @@
         <v>96</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>231</v>
+        <v>205</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>232</v>
+        <v>220</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>233</v>
+        <v>221</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>234</v>
+        <v>222</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
@@ -4072,13 +4108,13 @@
         <v>82</v>
       </c>
       <c r="X18" t="s" s="2">
-        <v>82</v>
+        <v>223</v>
       </c>
       <c r="Y18" t="s" s="2">
-        <v>82</v>
+        <v>224</v>
       </c>
       <c r="Z18" t="s" s="2">
-        <v>82</v>
+        <v>225</v>
       </c>
       <c r="AA18" t="s" s="2">
         <v>82</v>
@@ -4096,13 +4132,13 @@
         <v>82</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>229</v>
+        <v>218</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="AI18" t="s" s="2">
         <v>82</v>
@@ -4111,33 +4147,33 @@
         <v>107</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>235</v>
+        <v>82</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>236</v>
+        <v>226</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>237</v>
+        <v>227</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>82</v>
+        <v>228</v>
       </c>
       <c r="AO18" t="s" s="2">
-        <v>238</v>
+        <v>215</v>
       </c>
       <c r="AP18" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AQ18" t="s" s="2">
-        <v>82</v>
+        <v>229</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>239</v>
+        <v>230</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>239</v>
+        <v>230</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4145,13 +4181,13 @@
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="H19" t="s" s="2">
-        <v>96</v>
+        <v>82</v>
       </c>
       <c r="I19" t="s" s="2">
         <v>82</v>
@@ -4160,17 +4196,15 @@
         <v>96</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>240</v>
+        <v>231</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>241</v>
+        <v>232</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>242</v>
-      </c>
-      <c r="N19" t="s" s="2">
-        <v>243</v>
-      </c>
+        <v>233</v>
+      </c>
+      <c r="N19" s="2"/>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
         <v>82</v>
@@ -4219,13 +4253,13 @@
         <v>82</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>239</v>
+        <v>230</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="AI19" t="s" s="2">
         <v>82</v>
@@ -4234,37 +4268,37 @@
         <v>107</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>244</v>
+        <v>234</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>245</v>
+        <v>235</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>246</v>
+        <v>236</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>247</v>
+        <v>237</v>
       </c>
       <c r="AO19" t="s" s="2">
-        <v>82</v>
+        <v>238</v>
       </c>
       <c r="AP19" t="s" s="2">
-        <v>248</v>
+        <v>239</v>
       </c>
       <c r="AQ19" t="s" s="2">
-        <v>249</v>
+        <v>240</v>
       </c>
     </row>
-    <row r="20" hidden="true">
+    <row r="20">
       <c r="A20" t="s" s="2">
-        <v>250</v>
+        <v>241</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>250</v>
+        <v>241</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>82</v>
+        <v>242</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
@@ -4274,25 +4308,25 @@
         <v>95</v>
       </c>
       <c r="H20" t="s" s="2">
-        <v>82</v>
+        <v>96</v>
       </c>
       <c r="I20" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>82</v>
+        <v>96</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>251</v>
+        <v>243</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>252</v>
+        <v>244</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>253</v>
+        <v>245</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>254</v>
+        <v>246</v>
       </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
@@ -4342,7 +4376,7 @@
         <v>82</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>250</v>
+        <v>241</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>83</v>
@@ -4357,33 +4391,33 @@
         <v>107</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>256</v>
+        <v>249</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>257</v>
+        <v>82</v>
       </c>
       <c r="AO20" t="s" s="2">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="AP20" t="s" s="2">
-        <v>259</v>
+        <v>82</v>
       </c>
       <c r="AQ20" t="s" s="2">
-        <v>260</v>
+        <v>82</v>
       </c>
     </row>
-    <row r="21" hidden="true">
+    <row r="21">
       <c r="A21" t="s" s="2">
-        <v>261</v>
+        <v>251</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>261</v>
+        <v>251</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4394,28 +4428,28 @@
         <v>83</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="H21" t="s" s="2">
-        <v>82</v>
+        <v>96</v>
       </c>
       <c r="I21" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>82</v>
+        <v>96</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>262</v>
+        <v>252</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>263</v>
+        <v>253</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>264</v>
+        <v>254</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>265</v>
+        <v>255</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -4465,13 +4499,13 @@
         <v>82</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>261</v>
+        <v>251</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="AI21" t="s" s="2">
         <v>82</v>
@@ -4480,33 +4514,33 @@
         <v>107</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>244</v>
+        <v>256</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>266</v>
+        <v>257</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>267</v>
+        <v>258</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>82</v>
+        <v>259</v>
       </c>
       <c r="AO21" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP21" t="s" s="2">
-        <v>82</v>
+        <v>260</v>
       </c>
       <c r="AQ21" t="s" s="2">
-        <v>82</v>
+        <v>261</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>268</v>
+        <v>262</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>268</v>
+        <v>262</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4517,28 +4551,28 @@
         <v>83</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="H22" t="s" s="2">
-        <v>96</v>
+        <v>82</v>
       </c>
       <c r="I22" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>96</v>
+        <v>82</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>270</v>
+        <v>264</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>271</v>
+        <v>265</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -4588,13 +4622,13 @@
         <v>82</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>268</v>
+        <v>262</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="AI22" t="s" s="2">
         <v>82</v>
@@ -4603,33 +4637,33 @@
         <v>107</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>82</v>
+        <v>256</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>82</v>
+        <v>269</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>82</v>
+        <v>270</v>
       </c>
       <c r="AP22" t="s" s="2">
-        <v>82</v>
+        <v>271</v>
       </c>
       <c r="AQ22" t="s" s="2">
-        <v>275</v>
+        <v>272</v>
       </c>
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4652,15 +4686,17 @@
         <v>82</v>
       </c>
       <c r="K23" t="s" s="2">
+        <v>274</v>
+      </c>
+      <c r="L23" t="s" s="2">
+        <v>275</v>
+      </c>
+      <c r="M23" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="N23" t="s" s="2">
         <v>277</v>
       </c>
-      <c r="L23" t="s" s="2">
-        <v>278</v>
-      </c>
-      <c r="M23" t="s" s="2">
-        <v>279</v>
-      </c>
-      <c r="N23" s="2"/>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
         <v>82</v>
@@ -4709,7 +4745,7 @@
         <v>82</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>280</v>
+        <v>273</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>83</v>
@@ -4721,16 +4757,16 @@
         <v>82</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>82</v>
+        <v>107</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>82</v>
+        <v>256</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>82</v>
+        <v>278</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="AN23" t="s" s="2">
         <v>82</v>
@@ -4745,16 +4781,16 @@
         <v>82</v>
       </c>
     </row>
-    <row r="24" hidden="true">
+    <row r="24">
       <c r="A24" t="s" s="2">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>140</v>
+        <v>82</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
@@ -4764,25 +4800,25 @@
         <v>84</v>
       </c>
       <c r="H24" t="s" s="2">
-        <v>82</v>
+        <v>96</v>
       </c>
       <c r="I24" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>82</v>
+        <v>96</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>141</v>
+        <v>281</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>142</v>
+        <v>282</v>
       </c>
       <c r="M24" t="s" s="2">
         <v>283</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>144</v>
+        <v>284</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
@@ -4832,7 +4868,7 @@
         <v>82</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>83</v>
@@ -4844,16 +4880,16 @@
         <v>82</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>146</v>
+        <v>107</v>
       </c>
       <c r="AK24" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>82</v>
+        <v>285</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="AN24" t="s" s="2">
         <v>82</v>
@@ -4865,51 +4901,47 @@
         <v>82</v>
       </c>
       <c r="AQ24" t="s" s="2">
-        <v>82</v>
+        <v>287</v>
       </c>
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>286</v>
+        <v>82</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I25" t="s" s="2">
-        <v>96</v>
+        <v>82</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>96</v>
+        <v>82</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>141</v>
+        <v>289</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>288</v>
-      </c>
-      <c r="N25" t="s" s="2">
-        <v>144</v>
-      </c>
-      <c r="O25" t="s" s="2">
-        <v>289</v>
-      </c>
+        <v>291</v>
+      </c>
+      <c r="N25" s="2"/>
+      <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
         <v>82</v>
       </c>
@@ -4957,19 +4989,19 @@
         <v>82</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>146</v>
+        <v>82</v>
       </c>
       <c r="AK25" t="s" s="2">
         <v>82</v>
@@ -4978,7 +5010,7 @@
         <v>82</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>138</v>
+        <v>293</v>
       </c>
       <c r="AN25" t="s" s="2">
         <v>82</v>
@@ -4995,21 +5027,21 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>82</v>
+        <v>140</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>82</v>
@@ -5018,19 +5050,19 @@
         <v>82</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>96</v>
+        <v>82</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>115</v>
+        <v>141</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>292</v>
+        <v>142</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>294</v>
+        <v>144</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
@@ -5056,52 +5088,52 @@
         <v>82</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>175</v>
+        <v>82</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>295</v>
+        <v>82</v>
       </c>
       <c r="Z26" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA26" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB26" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC26" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD26" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE26" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF26" t="s" s="2">
         <v>296</v>
       </c>
-      <c r="AA26" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB26" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC26" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD26" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE26" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF26" t="s" s="2">
-        <v>291</v>
-      </c>
       <c r="AG26" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>107</v>
+        <v>146</v>
       </c>
       <c r="AK26" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>297</v>
+        <v>82</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>298</v>
+        <v>293</v>
       </c>
       <c r="AN26" t="s" s="2">
         <v>82</v>
@@ -5113,47 +5145,51 @@
         <v>82</v>
       </c>
       <c r="AQ26" t="s" s="2">
-        <v>299</v>
+        <v>82</v>
       </c>
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>82</v>
+        <v>298</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I27" t="s" s="2">
-        <v>82</v>
+        <v>96</v>
       </c>
       <c r="J27" t="s" s="2">
         <v>96</v>
       </c>
       <c r="K27" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="L27" t="s" s="2">
+        <v>299</v>
+      </c>
+      <c r="M27" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="N27" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="O27" t="s" s="2">
         <v>301</v>
       </c>
-      <c r="L27" t="s" s="2">
-        <v>302</v>
-      </c>
-      <c r="M27" t="s" s="2">
-        <v>303</v>
-      </c>
-      <c r="N27" s="2"/>
-      <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>82</v>
       </c>
@@ -5201,28 +5237,28 @@
         <v>82</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="AG27" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>107</v>
+        <v>146</v>
       </c>
       <c r="AK27" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>304</v>
+        <v>82</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>305</v>
+        <v>138</v>
       </c>
       <c r="AN27" t="s" s="2">
         <v>82</v>
@@ -5234,15 +5270,15 @@
         <v>82</v>
       </c>
       <c r="AQ27" t="s" s="2">
-        <v>306</v>
+        <v>82</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5250,7 +5286,7 @@
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="G28" t="s" s="2">
         <v>95</v>
@@ -5265,20 +5301,18 @@
         <v>96</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>277</v>
+        <v>115</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>310</v>
-      </c>
-      <c r="O28" t="s" s="2">
-        <v>311</v>
-      </c>
+        <v>306</v>
+      </c>
+      <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>82</v>
       </c>
@@ -5302,13 +5336,13 @@
         <v>82</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>82</v>
+        <v>187</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>82</v>
+        <v>307</v>
       </c>
       <c r="Z28" t="s" s="2">
-        <v>82</v>
+        <v>308</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>82</v>
@@ -5326,10 +5360,10 @@
         <v>82</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="AG28" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="AH28" t="s" s="2">
         <v>95</v>
@@ -5344,30 +5378,30 @@
         <v>82</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>82</v>
+        <v>309</v>
       </c>
       <c r="AM28" t="s" s="2">
+        <v>310</v>
+      </c>
+      <c r="AN28" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO28" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP28" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ28" t="s" s="2">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="29" hidden="true">
+      <c r="A29" t="s" s="2">
         <v>312</v>
       </c>
-      <c r="AN28" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO28" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP28" t="s" s="2">
-        <v>313</v>
-      </c>
-      <c r="AQ28" t="s" s="2">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="s" s="2">
-        <v>315</v>
-      </c>
       <c r="B29" t="s" s="2">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5375,13 +5409,13 @@
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="H29" t="s" s="2">
-        <v>96</v>
+        <v>82</v>
       </c>
       <c r="I29" t="s" s="2">
         <v>82</v>
@@ -5390,20 +5424,16 @@
         <v>96</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>193</v>
+        <v>313</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>317</v>
-      </c>
-      <c r="N29" t="s" s="2">
-        <v>318</v>
-      </c>
-      <c r="O29" t="s" s="2">
-        <v>319</v>
-      </c>
+        <v>315</v>
+      </c>
+      <c r="N29" s="2"/>
+      <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>82</v>
       </c>
@@ -5427,13 +5457,13 @@
         <v>82</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>320</v>
+        <v>82</v>
       </c>
       <c r="Y29" t="s" s="2">
-        <v>321</v>
+        <v>82</v>
       </c>
       <c r="Z29" t="s" s="2">
-        <v>322</v>
+        <v>82</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>82</v>
@@ -5451,13 +5481,13 @@
         <v>82</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="AG29" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>82</v>
@@ -5469,30 +5499,30 @@
         <v>82</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>324</v>
+        <v>317</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>325</v>
+        <v>82</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP29" t="s" s="2">
-        <v>326</v>
+        <v>82</v>
       </c>
       <c r="AQ29" t="s" s="2">
-        <v>327</v>
+        <v>318</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>328</v>
+        <v>319</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>328</v>
+        <v>319</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5500,7 +5530,7 @@
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="G30" t="s" s="2">
         <v>95</v>
@@ -5515,16 +5545,20 @@
         <v>96</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>269</v>
+        <v>289</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>329</v>
+        <v>320</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>330</v>
-      </c>
-      <c r="N30" s="2"/>
-      <c r="O30" s="2"/>
+        <v>321</v>
+      </c>
+      <c r="N30" t="s" s="2">
+        <v>322</v>
+      </c>
+      <c r="O30" t="s" s="2">
+        <v>323</v>
+      </c>
       <c r="P30" t="s" s="2">
         <v>82</v>
       </c>
@@ -5572,13 +5606,13 @@
         <v>82</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>328</v>
+        <v>319</v>
       </c>
       <c r="AG30" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH30" t="s" s="2">
         <v>95</v>
-      </c>
-      <c r="AH30" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>82</v>
@@ -5590,10 +5624,10 @@
         <v>82</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>331</v>
+        <v>82</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>332</v>
+        <v>324</v>
       </c>
       <c r="AN30" t="s" s="2">
         <v>82</v>
@@ -5602,18 +5636,18 @@
         <v>82</v>
       </c>
       <c r="AP30" t="s" s="2">
-        <v>82</v>
+        <v>325</v>
       </c>
       <c r="AQ30" t="s" s="2">
-        <v>82</v>
+        <v>326</v>
       </c>
     </row>
-    <row r="31" hidden="true">
+    <row r="31">
       <c r="A31" t="s" s="2">
-        <v>333</v>
+        <v>327</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>333</v>
+        <v>327</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5624,28 +5658,32 @@
         <v>83</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="H31" t="s" s="2">
-        <v>82</v>
+        <v>96</v>
       </c>
       <c r="I31" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>82</v>
+        <v>96</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>277</v>
+        <v>205</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>278</v>
+        <v>328</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>279</v>
-      </c>
-      <c r="N31" s="2"/>
-      <c r="O31" s="2"/>
+        <v>329</v>
+      </c>
+      <c r="N31" t="s" s="2">
+        <v>330</v>
+      </c>
+      <c r="O31" t="s" s="2">
+        <v>331</v>
+      </c>
       <c r="P31" t="s" s="2">
         <v>82</v>
       </c>
@@ -5669,13 +5707,13 @@
         <v>82</v>
       </c>
       <c r="X31" t="s" s="2">
-        <v>82</v>
+        <v>332</v>
       </c>
       <c r="Y31" t="s" s="2">
-        <v>82</v>
+        <v>333</v>
       </c>
       <c r="Z31" t="s" s="2">
-        <v>82</v>
+        <v>334</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>82</v>
@@ -5693,59 +5731,59 @@
         <v>82</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>280</v>
+        <v>327</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>82</v>
+        <v>107</v>
       </c>
       <c r="AK31" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>82</v>
+        <v>335</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>281</v>
+        <v>336</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>82</v>
+        <v>337</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP31" t="s" s="2">
-        <v>82</v>
+        <v>338</v>
       </c>
       <c r="AQ31" t="s" s="2">
-        <v>82</v>
+        <v>339</v>
       </c>
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>334</v>
+        <v>340</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>334</v>
+        <v>340</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>140</v>
+        <v>82</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>82</v>
@@ -5754,20 +5792,18 @@
         <v>82</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>82</v>
+        <v>96</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>141</v>
+        <v>281</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>142</v>
+        <v>341</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>283</v>
-      </c>
-      <c r="N32" t="s" s="2">
-        <v>144</v>
-      </c>
+        <v>342</v>
+      </c>
+      <c r="N32" s="2"/>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
         <v>82</v>
@@ -5816,10 +5852,10 @@
         <v>82</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>284</v>
+        <v>340</v>
       </c>
       <c r="AG32" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="AH32" t="s" s="2">
         <v>84</v>
@@ -5828,16 +5864,16 @@
         <v>82</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>146</v>
+        <v>107</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>82</v>
+        <v>343</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>281</v>
+        <v>344</v>
       </c>
       <c r="AN32" t="s" s="2">
         <v>82</v>
@@ -5854,46 +5890,42 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>335</v>
+        <v>345</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>335</v>
+        <v>345</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>286</v>
+        <v>82</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I33" t="s" s="2">
-        <v>96</v>
+        <v>82</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>96</v>
+        <v>82</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>141</v>
+        <v>289</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>288</v>
-      </c>
-      <c r="N33" t="s" s="2">
-        <v>144</v>
-      </c>
-      <c r="O33" t="s" s="2">
-        <v>289</v>
-      </c>
+        <v>291</v>
+      </c>
+      <c r="N33" s="2"/>
+      <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
         <v>82</v>
       </c>
@@ -5941,19 +5973,19 @@
         <v>82</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>146</v>
+        <v>82</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>82</v>
@@ -5962,7 +5994,7 @@
         <v>82</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>138</v>
+        <v>293</v>
       </c>
       <c r="AN33" t="s" s="2">
         <v>82</v>
@@ -5979,21 +6011,21 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>336</v>
+        <v>346</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>336</v>
+        <v>346</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>82</v>
+        <v>140</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>82</v>
@@ -6002,18 +6034,20 @@
         <v>82</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>96</v>
+        <v>82</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>337</v>
+        <v>141</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>338</v>
+        <v>142</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>339</v>
-      </c>
-      <c r="N34" s="2"/>
+        <v>295</v>
+      </c>
+      <c r="N34" t="s" s="2">
+        <v>144</v>
+      </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>82</v>
@@ -6062,80 +6096,84 @@
         <v>82</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>336</v>
+        <v>296</v>
       </c>
       <c r="AG34" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>107</v>
+        <v>146</v>
       </c>
       <c r="AK34" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>340</v>
+        <v>82</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>332</v>
+        <v>293</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>341</v>
+        <v>82</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP34" t="s" s="2">
-        <v>342</v>
+        <v>82</v>
       </c>
       <c r="AQ34" t="s" s="2">
-        <v>343</v>
+        <v>82</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>82</v>
+        <v>298</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I35" t="s" s="2">
-        <v>82</v>
+        <v>96</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>82</v>
+        <v>96</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>277</v>
+        <v>141</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>278</v>
+        <v>299</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>279</v>
-      </c>
-      <c r="N35" s="2"/>
-      <c r="O35" s="2"/>
+        <v>300</v>
+      </c>
+      <c r="N35" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="O35" t="s" s="2">
+        <v>301</v>
+      </c>
       <c r="P35" t="s" s="2">
         <v>82</v>
       </c>
@@ -6183,19 +6221,19 @@
         <v>82</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>280</v>
+        <v>302</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="AI35" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>82</v>
+        <v>146</v>
       </c>
       <c r="AK35" t="s" s="2">
         <v>82</v>
@@ -6204,7 +6242,7 @@
         <v>82</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>281</v>
+        <v>138</v>
       </c>
       <c r="AN35" t="s" s="2">
         <v>82</v>
@@ -6221,21 +6259,21 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>140</v>
+        <v>82</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>82</v>
@@ -6244,20 +6282,18 @@
         <v>82</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>82</v>
+        <v>96</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>141</v>
+        <v>349</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>142</v>
+        <v>350</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>283</v>
-      </c>
-      <c r="N36" t="s" s="2">
-        <v>144</v>
-      </c>
+        <v>351</v>
+      </c>
+      <c r="N36" s="2"/>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>82</v>
@@ -6294,60 +6330,60 @@
         <v>82</v>
       </c>
       <c r="AB36" t="s" s="2">
-        <v>346</v>
+        <v>82</v>
       </c>
       <c r="AC36" t="s" s="2">
-        <v>347</v>
+        <v>82</v>
       </c>
       <c r="AD36" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE36" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF36" t="s" s="2">
         <v>348</v>
       </c>
-      <c r="AF36" t="s" s="2">
-        <v>284</v>
-      </c>
       <c r="AG36" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>146</v>
+        <v>107</v>
       </c>
       <c r="AK36" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>82</v>
+        <v>352</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>281</v>
+        <v>344</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>82</v>
+        <v>353</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP36" t="s" s="2">
-        <v>82</v>
+        <v>354</v>
       </c>
       <c r="AQ36" t="s" s="2">
-        <v>82</v>
+        <v>355</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>349</v>
+        <v>356</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>349</v>
+        <v>356</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6355,7 +6391,7 @@
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="G37" t="s" s="2">
         <v>95</v>
@@ -6367,21 +6403,19 @@
         <v>82</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>96</v>
+        <v>82</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>115</v>
+        <v>289</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>350</v>
+        <v>290</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>351</v>
+        <v>291</v>
       </c>
       <c r="N37" s="2"/>
-      <c r="O37" t="s" s="2">
-        <v>352</v>
-      </c>
+      <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>82</v>
       </c>
@@ -6393,7 +6427,7 @@
         <v>82</v>
       </c>
       <c r="T37" t="s" s="2">
-        <v>353</v>
+        <v>82</v>
       </c>
       <c r="U37" t="s" s="2">
         <v>82</v>
@@ -6405,13 +6439,13 @@
         <v>82</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>175</v>
+        <v>82</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>354</v>
+        <v>82</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>355</v>
+        <v>82</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>82</v>
@@ -6429,7 +6463,7 @@
         <v>82</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>356</v>
+        <v>292</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>83</v>
@@ -6441,7 +6475,7 @@
         <v>82</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>107</v>
+        <v>82</v>
       </c>
       <c r="AK37" t="s" s="2">
         <v>82</v>
@@ -6450,61 +6484,61 @@
         <v>82</v>
       </c>
       <c r="AM37" t="s" s="2">
+        <v>293</v>
+      </c>
+      <c r="AN37" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO37" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP37" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ37" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="38" hidden="true">
+      <c r="A38" t="s" s="2">
         <v>357</v>
       </c>
-      <c r="AN37" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO37" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP37" t="s" s="2">
-        <v>358</v>
-      </c>
-      <c r="AQ37" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="s" s="2">
-        <v>359</v>
-      </c>
       <c r="B38" t="s" s="2">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>82</v>
+        <v>140</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="H38" t="s" s="2">
-        <v>96</v>
+        <v>82</v>
       </c>
       <c r="I38" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>96</v>
+        <v>82</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>115</v>
+        <v>141</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>360</v>
+        <v>142</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>361</v>
-      </c>
-      <c r="N38" s="2"/>
-      <c r="O38" t="s" s="2">
-        <v>362</v>
-      </c>
+        <v>295</v>
+      </c>
+      <c r="N38" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>82</v>
       </c>
@@ -6516,7 +6550,7 @@
         <v>82</v>
       </c>
       <c r="T38" t="s" s="2">
-        <v>363</v>
+        <v>82</v>
       </c>
       <c r="U38" t="s" s="2">
         <v>82</v>
@@ -6528,43 +6562,43 @@
         <v>82</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>119</v>
+        <v>82</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>121</v>
+        <v>82</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB38" t="s" s="2">
-        <v>82</v>
+        <v>358</v>
       </c>
       <c r="AC38" t="s" s="2">
-        <v>82</v>
+        <v>359</v>
       </c>
       <c r="AD38" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE38" t="s" s="2">
-        <v>82</v>
+        <v>168</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>364</v>
+        <v>296</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>107</v>
+        <v>146</v>
       </c>
       <c r="AK38" t="s" s="2">
         <v>82</v>
@@ -6573,7 +6607,7 @@
         <v>82</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>365</v>
+        <v>293</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>82</v>
@@ -6590,10 +6624,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>366</v>
+        <v>360</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>366</v>
+        <v>360</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6613,22 +6647,20 @@
         <v>82</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>82</v>
+        <v>96</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>367</v>
+        <v>115</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>368</v>
+        <v>361</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>369</v>
-      </c>
-      <c r="N39" t="s" s="2">
-        <v>370</v>
-      </c>
+        <v>362</v>
+      </c>
+      <c r="N39" s="2"/>
       <c r="O39" t="s" s="2">
-        <v>371</v>
+        <v>363</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>82</v>
@@ -6641,7 +6673,7 @@
         <v>82</v>
       </c>
       <c r="T39" t="s" s="2">
-        <v>82</v>
+        <v>364</v>
       </c>
       <c r="U39" t="s" s="2">
         <v>82</v>
@@ -6653,13 +6685,13 @@
         <v>82</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>82</v>
+        <v>187</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>82</v>
+        <v>365</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>82</v>
+        <v>366</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>82</v>
@@ -6677,7 +6709,7 @@
         <v>82</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>372</v>
+        <v>367</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>83</v>
@@ -6698,7 +6730,7 @@
         <v>82</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>373</v>
+        <v>368</v>
       </c>
       <c r="AN39" t="s" s="2">
         <v>82</v>
@@ -6707,18 +6739,18 @@
         <v>82</v>
       </c>
       <c r="AP39" t="s" s="2">
-        <v>374</v>
+        <v>369</v>
       </c>
       <c r="AQ39" t="s" s="2">
         <v>82</v>
       </c>
     </row>
-    <row r="40" hidden="true">
+    <row r="40">
       <c r="A40" t="s" s="2">
-        <v>375</v>
+        <v>370</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>375</v>
+        <v>370</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6729,10 +6761,10 @@
         <v>83</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="H40" t="s" s="2">
-        <v>82</v>
+        <v>96</v>
       </c>
       <c r="I40" t="s" s="2">
         <v>82</v>
@@ -6741,19 +6773,17 @@
         <v>96</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>376</v>
+        <v>115</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>377</v>
+        <v>371</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>378</v>
-      </c>
-      <c r="N40" t="s" s="2">
-        <v>379</v>
-      </c>
+        <v>372</v>
+      </c>
+      <c r="N40" s="2"/>
       <c r="O40" t="s" s="2">
-        <v>380</v>
+        <v>373</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>82</v>
@@ -6766,7 +6796,7 @@
         <v>82</v>
       </c>
       <c r="T40" t="s" s="2">
-        <v>381</v>
+        <v>374</v>
       </c>
       <c r="U40" t="s" s="2">
         <v>82</v>
@@ -6778,13 +6808,13 @@
         <v>82</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>82</v>
+        <v>119</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>82</v>
+        <v>121</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>82</v>
@@ -6802,7 +6832,7 @@
         <v>82</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>382</v>
+        <v>375</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>83</v>
@@ -6823,7 +6853,7 @@
         <v>82</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>383</v>
+        <v>376</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>82</v>
@@ -6832,7 +6862,7 @@
         <v>82</v>
       </c>
       <c r="AP40" t="s" s="2">
-        <v>384</v>
+        <v>82</v>
       </c>
       <c r="AQ40" t="s" s="2">
         <v>82</v>
@@ -6840,10 +6870,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>385</v>
+        <v>377</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>385</v>
+        <v>377</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6851,7 +6881,7 @@
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="G41" t="s" s="2">
         <v>95</v>
@@ -6863,22 +6893,22 @@
         <v>82</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>96</v>
+        <v>82</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>386</v>
+        <v>378</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>387</v>
+        <v>379</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>388</v>
+        <v>380</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>389</v>
+        <v>381</v>
       </c>
       <c r="O41" t="s" s="2">
-        <v>390</v>
+        <v>382</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>82</v>
@@ -6927,7 +6957,7 @@
         <v>82</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>391</v>
+        <v>383</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>83</v>
@@ -6948,7 +6978,7 @@
         <v>82</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>392</v>
+        <v>384</v>
       </c>
       <c r="AN41" t="s" s="2">
         <v>82</v>
@@ -6957,7 +6987,7 @@
         <v>82</v>
       </c>
       <c r="AP41" t="s" s="2">
-        <v>82</v>
+        <v>385</v>
       </c>
       <c r="AQ41" t="s" s="2">
         <v>82</v>
@@ -6965,10 +6995,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>393</v>
+        <v>386</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>393</v>
+        <v>386</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6979,7 +7009,7 @@
         <v>83</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>82</v>
@@ -6991,19 +7021,19 @@
         <v>96</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>367</v>
+        <v>387</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>394</v>
+        <v>388</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>395</v>
+        <v>389</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>396</v>
+        <v>390</v>
       </c>
       <c r="O42" t="s" s="2">
-        <v>397</v>
+        <v>391</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>82</v>
@@ -7016,7 +7046,7 @@
         <v>82</v>
       </c>
       <c r="T42" t="s" s="2">
-        <v>82</v>
+        <v>392</v>
       </c>
       <c r="U42" t="s" s="2">
         <v>82</v>
@@ -7052,7 +7082,7 @@
         <v>82</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>398</v>
+        <v>393</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>83</v>
@@ -7073,7 +7103,7 @@
         <v>82</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>399</v>
+        <v>394</v>
       </c>
       <c r="AN42" t="s" s="2">
         <v>82</v>
@@ -7082,7 +7112,7 @@
         <v>82</v>
       </c>
       <c r="AP42" t="s" s="2">
-        <v>82</v>
+        <v>395</v>
       </c>
       <c r="AQ42" t="s" s="2">
         <v>82</v>
@@ -7090,10 +7120,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>400</v>
+        <v>396</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>400</v>
+        <v>396</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7116,17 +7146,19 @@
         <v>96</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>277</v>
+        <v>397</v>
       </c>
       <c r="L43" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="M43" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="N43" t="s" s="2">
+        <v>400</v>
+      </c>
+      <c r="O43" t="s" s="2">
         <v>401</v>
-      </c>
-      <c r="M43" t="s" s="2">
-        <v>402</v>
-      </c>
-      <c r="N43" s="2"/>
-      <c r="O43" t="s" s="2">
-        <v>403</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>82</v>
@@ -7139,7 +7171,7 @@
         <v>82</v>
       </c>
       <c r="T43" t="s" s="2">
-        <v>404</v>
+        <v>82</v>
       </c>
       <c r="U43" t="s" s="2">
         <v>82</v>
@@ -7175,7 +7207,7 @@
         <v>82</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>83</v>
@@ -7196,7 +7228,7 @@
         <v>82</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="AN43" t="s" s="2">
         <v>82</v>
@@ -7211,12 +7243,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="44">
+    <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7230,7 +7262,7 @@
         <v>95</v>
       </c>
       <c r="H44" t="s" s="2">
-        <v>96</v>
+        <v>82</v>
       </c>
       <c r="I44" t="s" s="2">
         <v>82</v>
@@ -7239,17 +7271,19 @@
         <v>96</v>
       </c>
       <c r="K44" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="L44" t="s" s="2">
+        <v>405</v>
+      </c>
+      <c r="M44" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="N44" t="s" s="2">
+        <v>407</v>
+      </c>
+      <c r="O44" t="s" s="2">
         <v>408</v>
-      </c>
-      <c r="L44" t="s" s="2">
-        <v>409</v>
-      </c>
-      <c r="M44" t="s" s="2">
-        <v>410</v>
-      </c>
-      <c r="N44" s="2"/>
-      <c r="O44" t="s" s="2">
-        <v>411</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>82</v>
@@ -7298,7 +7332,7 @@
         <v>82</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>83</v>
@@ -7319,7 +7353,7 @@
         <v>82</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>392</v>
+        <v>410</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>82</v>
@@ -7334,12 +7368,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="45">
+    <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7353,7 +7387,7 @@
         <v>95</v>
       </c>
       <c r="H45" t="s" s="2">
-        <v>96</v>
+        <v>82</v>
       </c>
       <c r="I45" t="s" s="2">
         <v>82</v>
@@ -7362,18 +7396,18 @@
         <v>96</v>
       </c>
       <c r="K45" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="L45" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="M45" t="s" s="2">
+        <v>413</v>
+      </c>
+      <c r="N45" s="2"/>
+      <c r="O45" t="s" s="2">
         <v>414</v>
       </c>
-      <c r="L45" t="s" s="2">
-        <v>415</v>
-      </c>
-      <c r="M45" t="s" s="2">
-        <v>416</v>
-      </c>
-      <c r="N45" t="s" s="2">
-        <v>417</v>
-      </c>
-      <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>82</v>
       </c>
@@ -7385,7 +7419,7 @@
         <v>82</v>
       </c>
       <c r="T45" t="s" s="2">
-        <v>82</v>
+        <v>415</v>
       </c>
       <c r="U45" t="s" s="2">
         <v>82</v>
@@ -7397,13 +7431,13 @@
         <v>82</v>
       </c>
       <c r="X45" t="s" s="2">
-        <v>119</v>
+        <v>82</v>
       </c>
       <c r="Y45" t="s" s="2">
-        <v>418</v>
+        <v>82</v>
       </c>
       <c r="Z45" t="s" s="2">
-        <v>419</v>
+        <v>82</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>82</v>
@@ -7421,7 +7455,7 @@
         <v>82</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>83</v>
@@ -7439,13 +7473,13 @@
         <v>82</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>420</v>
+        <v>82</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>332</v>
+        <v>417</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>421</v>
+        <v>82</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>82</v>
@@ -7454,15 +7488,15 @@
         <v>82</v>
       </c>
       <c r="AQ45" t="s" s="2">
-        <v>422</v>
+        <v>82</v>
       </c>
     </row>
-    <row r="46" hidden="true">
+    <row r="46">
       <c r="A46" t="s" s="2">
-        <v>423</v>
+        <v>418</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>423</v>
+        <v>418</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7476,7 +7510,7 @@
         <v>95</v>
       </c>
       <c r="H46" t="s" s="2">
-        <v>82</v>
+        <v>96</v>
       </c>
       <c r="I46" t="s" s="2">
         <v>82</v>
@@ -7485,18 +7519,18 @@
         <v>96</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>269</v>
+        <v>419</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>424</v>
+        <v>420</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>425</v>
-      </c>
-      <c r="N46" t="s" s="2">
-        <v>426</v>
-      </c>
-      <c r="O46" s="2"/>
+        <v>421</v>
+      </c>
+      <c r="N46" s="2"/>
+      <c r="O46" t="s" s="2">
+        <v>422</v>
+      </c>
       <c r="P46" t="s" s="2">
         <v>82</v>
       </c>
@@ -7565,7 +7599,7 @@
         <v>82</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>427</v>
+        <v>403</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>82</v>
@@ -7580,12 +7614,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="47" hidden="true">
+    <row r="47">
       <c r="A47" t="s" s="2">
-        <v>428</v>
+        <v>424</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>428</v>
+        <v>424</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7599,24 +7633,26 @@
         <v>95</v>
       </c>
       <c r="H47" t="s" s="2">
-        <v>82</v>
+        <v>96</v>
       </c>
       <c r="I47" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>82</v>
+        <v>96</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>277</v>
+        <v>425</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>278</v>
+        <v>426</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>279</v>
-      </c>
-      <c r="N47" s="2"/>
+        <v>427</v>
+      </c>
+      <c r="N47" t="s" s="2">
+        <v>428</v>
+      </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
         <v>82</v>
@@ -7641,13 +7677,13 @@
         <v>82</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>82</v>
+        <v>119</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>82</v>
+        <v>429</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>82</v>
+        <v>430</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>82</v>
@@ -7665,7 +7701,7 @@
         <v>82</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>280</v>
+        <v>424</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>83</v>
@@ -7677,19 +7713,19 @@
         <v>82</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>82</v>
+        <v>107</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>82</v>
+        <v>431</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>281</v>
+        <v>344</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>82</v>
+        <v>432</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>82</v>
@@ -7698,26 +7734,26 @@
         <v>82</v>
       </c>
       <c r="AQ47" t="s" s="2">
-        <v>82</v>
+        <v>433</v>
       </c>
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>429</v>
+        <v>434</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>429</v>
+        <v>434</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>140</v>
+        <v>82</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>82</v>
@@ -7726,19 +7762,19 @@
         <v>82</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>82</v>
+        <v>96</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>141</v>
+        <v>281</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>142</v>
+        <v>435</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>283</v>
+        <v>436</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>144</v>
+        <v>437</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -7788,19 +7824,19 @@
         <v>82</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>284</v>
+        <v>434</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="AI48" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>146</v>
+        <v>107</v>
       </c>
       <c r="AK48" t="s" s="2">
         <v>82</v>
@@ -7809,7 +7845,7 @@
         <v>82</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>281</v>
+        <v>438</v>
       </c>
       <c r="AN48" t="s" s="2">
         <v>82</v>
@@ -7826,46 +7862,42 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>430</v>
+        <v>439</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>430</v>
+        <v>439</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>286</v>
+        <v>82</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I49" t="s" s="2">
-        <v>96</v>
+        <v>82</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>96</v>
+        <v>82</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>141</v>
+        <v>289</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>288</v>
-      </c>
-      <c r="N49" t="s" s="2">
-        <v>144</v>
-      </c>
-      <c r="O49" t="s" s="2">
-        <v>289</v>
-      </c>
+        <v>291</v>
+      </c>
+      <c r="N49" s="2"/>
+      <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>82</v>
       </c>
@@ -7913,19 +7945,19 @@
         <v>82</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>146</v>
+        <v>82</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>82</v>
@@ -7934,7 +7966,7 @@
         <v>82</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>138</v>
+        <v>293</v>
       </c>
       <c r="AN49" t="s" s="2">
         <v>82</v>
@@ -7951,14 +7983,14 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>431</v>
+        <v>440</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>431</v>
+        <v>440</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>82</v>
+        <v>140</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
@@ -7977,15 +8009,17 @@
         <v>82</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>432</v>
+        <v>141</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>433</v>
+        <v>142</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>434</v>
-      </c>
-      <c r="N50" s="2"/>
+        <v>295</v>
+      </c>
+      <c r="N50" t="s" s="2">
+        <v>144</v>
+      </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
         <v>82</v>
@@ -8034,7 +8068,7 @@
         <v>82</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>431</v>
+        <v>296</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>83</v>
@@ -8046,22 +8080,22 @@
         <v>82</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>107</v>
+        <v>146</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>435</v>
+        <v>82</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>436</v>
+        <v>82</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>437</v>
+        <v>293</v>
       </c>
       <c r="AN50" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>438</v>
+        <v>82</v>
       </c>
       <c r="AP50" t="s" s="2">
         <v>82</v>
@@ -8072,14 +8106,14 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>82</v>
+        <v>298</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
@@ -8092,24 +8126,26 @@
         <v>82</v>
       </c>
       <c r="I51" t="s" s="2">
-        <v>82</v>
+        <v>96</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>82</v>
+        <v>96</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>193</v>
+        <v>141</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>440</v>
+        <v>299</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>441</v>
+        <v>300</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>442</v>
-      </c>
-      <c r="O51" s="2"/>
+        <v>144</v>
+      </c>
+      <c r="O51" t="s" s="2">
+        <v>301</v>
+      </c>
       <c r="P51" t="s" s="2">
         <v>82</v>
       </c>
@@ -8133,13 +8169,13 @@
         <v>82</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>211</v>
+        <v>82</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>443</v>
+        <v>82</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>444</v>
+        <v>82</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>82</v>
@@ -8157,7 +8193,7 @@
         <v>82</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>439</v>
+        <v>302</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>83</v>
@@ -8169,16 +8205,16 @@
         <v>82</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>107</v>
+        <v>146</v>
       </c>
       <c r="AK51" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>445</v>
+        <v>82</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>446</v>
+        <v>138</v>
       </c>
       <c r="AN51" t="s" s="2">
         <v>82</v>
@@ -8190,15 +8226,15 @@
         <v>82</v>
       </c>
       <c r="AQ51" t="s" s="2">
-        <v>447</v>
+        <v>82</v>
       </c>
     </row>
-    <row r="52">
+    <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>448</v>
+        <v>442</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>448</v>
+        <v>442</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8209,25 +8245,25 @@
         <v>83</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="H52" t="s" s="2">
-        <v>96</v>
+        <v>82</v>
       </c>
       <c r="I52" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>96</v>
+        <v>82</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>449</v>
+        <v>443</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>450</v>
+        <v>444</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>451</v>
+        <v>445</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -8278,13 +8314,13 @@
         <v>82</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>448</v>
+        <v>442</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>82</v>
@@ -8293,33 +8329,33 @@
         <v>107</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>82</v>
+        <v>446</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>452</v>
+        <v>447</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>454</v>
+        <v>82</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>82</v>
+        <v>449</v>
       </c>
       <c r="AP52" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AQ52" t="s" s="2">
-        <v>455</v>
+        <v>82</v>
       </c>
     </row>
-    <row r="53">
+    <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>456</v>
+        <v>450</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>456</v>
+        <v>450</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8330,10 +8366,10 @@
         <v>83</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="H53" t="s" s="2">
-        <v>96</v>
+        <v>82</v>
       </c>
       <c r="I53" t="s" s="2">
         <v>82</v>
@@ -8342,15 +8378,17 @@
         <v>82</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>193</v>
+        <v>205</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>457</v>
+        <v>451</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>458</v>
-      </c>
-      <c r="N53" s="2"/>
+        <v>452</v>
+      </c>
+      <c r="N53" t="s" s="2">
+        <v>453</v>
+      </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>82</v>
@@ -8375,13 +8413,13 @@
         <v>82</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>211</v>
+        <v>223</v>
       </c>
       <c r="Y53" t="s" s="2">
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="Z53" t="s" s="2">
-        <v>460</v>
+        <v>455</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>82</v>
@@ -8399,13 +8437,13 @@
         <v>82</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>456</v>
+        <v>450</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>82</v>
@@ -8417,13 +8455,13 @@
         <v>82</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>461</v>
+        <v>456</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>462</v>
+        <v>457</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>463</v>
+        <v>82</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>82</v>
@@ -8432,15 +8470,15 @@
         <v>82</v>
       </c>
       <c r="AQ53" t="s" s="2">
-        <v>464</v>
+        <v>458</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>465</v>
+        <v>459</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>465</v>
+        <v>459</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8460,23 +8498,19 @@
         <v>82</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>82</v>
+        <v>96</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>193</v>
+        <v>460</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>466</v>
+        <v>461</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>467</v>
-      </c>
-      <c r="N54" t="s" s="2">
-        <v>468</v>
-      </c>
-      <c r="O54" t="s" s="2">
-        <v>469</v>
-      </c>
+        <v>462</v>
+      </c>
+      <c r="N54" s="2"/>
+      <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
         <v>82</v>
       </c>
@@ -8500,13 +8534,13 @@
         <v>82</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>211</v>
+        <v>82</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>470</v>
+        <v>82</v>
       </c>
       <c r="Z54" t="s" s="2">
-        <v>471</v>
+        <v>82</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>82</v>
@@ -8524,7 +8558,7 @@
         <v>82</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>465</v>
+        <v>459</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>83</v>
@@ -8542,13 +8576,13 @@
         <v>82</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>82</v>
@@ -8557,15 +8591,15 @@
         <v>82</v>
       </c>
       <c r="AQ54" t="s" s="2">
-        <v>472</v>
+        <v>466</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>473</v>
+        <v>467</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>473</v>
+        <v>467</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8588,13 +8622,13 @@
         <v>82</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>474</v>
+        <v>205</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>475</v>
+        <v>468</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>476</v>
+        <v>469</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -8621,13 +8655,13 @@
         <v>82</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>82</v>
+        <v>223</v>
       </c>
       <c r="Y55" t="s" s="2">
-        <v>82</v>
+        <v>470</v>
       </c>
       <c r="Z55" t="s" s="2">
-        <v>82</v>
+        <v>471</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>82</v>
@@ -8645,7 +8679,7 @@
         <v>82</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>473</v>
+        <v>467</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>83</v>
@@ -8663,13 +8697,13 @@
         <v>82</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>223</v>
+        <v>472</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>224</v>
+        <v>473</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>225</v>
+        <v>474</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>82</v>
@@ -8678,15 +8712,15 @@
         <v>82</v>
       </c>
       <c r="AQ55" t="s" s="2">
-        <v>477</v>
+        <v>475</v>
       </c>
     </row>
-    <row r="56" hidden="true">
+    <row r="56">
       <c r="A56" t="s" s="2">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8697,10 +8731,10 @@
         <v>83</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="H56" t="s" s="2">
-        <v>82</v>
+        <v>96</v>
       </c>
       <c r="I56" t="s" s="2">
         <v>82</v>
@@ -8709,18 +8743,20 @@
         <v>82</v>
       </c>
       <c r="K56" t="s" s="2">
+        <v>205</v>
+      </c>
+      <c r="L56" t="s" s="2">
+        <v>477</v>
+      </c>
+      <c r="M56" t="s" s="2">
+        <v>478</v>
+      </c>
+      <c r="N56" t="s" s="2">
         <v>479</v>
       </c>
-      <c r="L56" t="s" s="2">
+      <c r="O56" t="s" s="2">
         <v>480</v>
       </c>
-      <c r="M56" t="s" s="2">
-        <v>481</v>
-      </c>
-      <c r="N56" t="s" s="2">
-        <v>482</v>
-      </c>
-      <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
         <v>82</v>
       </c>
@@ -8744,13 +8780,13 @@
         <v>82</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>82</v>
+        <v>223</v>
       </c>
       <c r="Y56" t="s" s="2">
-        <v>82</v>
+        <v>481</v>
       </c>
       <c r="Z56" t="s" s="2">
-        <v>82</v>
+        <v>482</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>82</v>
@@ -8768,13 +8804,13 @@
         <v>82</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>82</v>
@@ -8786,26 +8822,270 @@
         <v>82</v>
       </c>
       <c r="AL56" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="AM56" t="s" s="2">
+        <v>473</v>
+      </c>
+      <c r="AN56" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="AO56" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP56" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ56" t="s" s="2">
         <v>483</v>
       </c>
-      <c r="AM56" t="s" s="2">
+    </row>
+    <row r="57">
+      <c r="A57" t="s" s="2">
         <v>484</v>
       </c>
-      <c r="AN56" t="s" s="2">
+      <c r="B57" t="s" s="2">
+        <v>484</v>
+      </c>
+      <c r="C57" s="2"/>
+      <c r="D57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E57" s="2"/>
+      <c r="F57" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="G57" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="H57" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="I57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K57" t="s" s="2">
         <v>485</v>
       </c>
-      <c r="AO56" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP56" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ56" t="s" s="2">
+      <c r="L57" t="s" s="2">
         <v>486</v>
+      </c>
+      <c r="M57" t="s" s="2">
+        <v>487</v>
+      </c>
+      <c r="N57" s="2"/>
+      <c r="O57" s="2"/>
+      <c r="P57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q57" s="2"/>
+      <c r="R57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF57" t="s" s="2">
+        <v>484</v>
+      </c>
+      <c r="AG57" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH57" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="AI57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ57" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="AK57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL57" t="s" s="2">
+        <v>235</v>
+      </c>
+      <c r="AM57" t="s" s="2">
+        <v>236</v>
+      </c>
+      <c r="AN57" t="s" s="2">
+        <v>237</v>
+      </c>
+      <c r="AO57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ57" t="s" s="2">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="58" hidden="true">
+      <c r="A58" t="s" s="2">
+        <v>489</v>
+      </c>
+      <c r="B58" t="s" s="2">
+        <v>489</v>
+      </c>
+      <c r="C58" s="2"/>
+      <c r="D58" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E58" s="2"/>
+      <c r="F58" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="G58" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H58" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I58" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J58" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K58" t="s" s="2">
+        <v>490</v>
+      </c>
+      <c r="L58" t="s" s="2">
+        <v>491</v>
+      </c>
+      <c r="M58" t="s" s="2">
+        <v>492</v>
+      </c>
+      <c r="N58" t="s" s="2">
+        <v>493</v>
+      </c>
+      <c r="O58" s="2"/>
+      <c r="P58" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q58" s="2"/>
+      <c r="R58" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S58" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T58" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U58" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V58" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W58" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X58" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y58" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z58" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA58" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB58" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC58" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD58" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE58" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF58" t="s" s="2">
+        <v>489</v>
+      </c>
+      <c r="AG58" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH58" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI58" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ58" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="AK58" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL58" t="s" s="2">
+        <v>494</v>
+      </c>
+      <c r="AM58" t="s" s="2">
+        <v>495</v>
+      </c>
+      <c r="AN58" t="s" s="2">
+        <v>496</v>
+      </c>
+      <c r="AO58" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP58" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ58" t="s" s="2">
+        <v>497</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AQ56">
+  <autoFilter ref="A1:AQ58">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -8815,7 +9095,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI55">
+  <conditionalFormatting sqref="A2:AI57">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/ITI/MHD/StructureDefinition-IHE.MHD.SimplifiedPublish.DocumentReference.xlsx
+++ b/ITI/MHD/StructureDefinition-IHE.MHD.SimplifiedPublish.DocumentReference.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>4.2.4</t>
+    <t>4.2.5-comment</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-15T14:55:16-05:00</t>
+    <t>2026-06-16T19:25:56-05:00</t>
   </si>
   <si>
     <t>Publisher</t>
